--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/машины ПОКОМ КИ ОПТЫ (26,08,26).xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/25,08,26 ПОКОМ КИ/машины ПОКОМ КИ ОПТЫ (26,08,26).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\25,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{423590B5-832B-41DA-A934-AF24C16698C7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94C7150-2091-4C73-94AF-1E525F9C8692}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
   <si>
     <t>ПОЛУЧАТЕЛЬ</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>2 машина на 30,08</t>
+  </si>
+  <si>
+    <t>уже забрали</t>
   </si>
 </sst>
 </file>
@@ -139,7 +142,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,6 +167,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="26">
     <border>
@@ -518,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -559,6 +568,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -583,13 +593,14 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -870,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -886,50 +897,51 @@
     <col min="14" max="15" width="7.28515625" customWidth="1"/>
     <col min="16" max="16" width="6" customWidth="1"/>
     <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="38" t="s">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="36" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="42"/>
       <c r="K1" s="43" t="s">
         <v>1</v>
       </c>
       <c r="L1" s="44"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="36" t="s">
+      <c r="M1" s="35"/>
+      <c r="N1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="40"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="34" t="s">
+      <c r="O1" s="41"/>
+      <c r="P1" s="42"/>
+      <c r="Q1" s="35" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
+    <row r="2" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="38"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
       <c r="E2" s="13" t="s">
         <v>5</v>
       </c>
@@ -966,9 +978,9 @@
       <c r="P2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="35"/>
+      <c r="Q2" s="36"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>12</v>
       </c>
@@ -999,7 +1011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>13</v>
       </c>
@@ -1014,7 +1026,7 @@
       <c r="E4" s="6"/>
       <c r="F4" s="20"/>
       <c r="G4" s="21"/>
-      <c r="H4" s="6">
+      <c r="H4" s="45">
         <v>1405</v>
       </c>
       <c r="I4" s="7"/>
@@ -1029,8 +1041,11 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="R4" s="46" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>18</v>
       </c>
@@ -1058,7 +1073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1067,7 +1082,7 @@
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="28">
-        <f t="shared" ref="D6:D7" si="1">B6+C6</f>
+        <f t="shared" ref="D6" si="1">B6+C6</f>
         <v>1537</v>
       </c>
       <c r="E6" s="19"/>
@@ -1089,7 +1104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
@@ -1117,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
@@ -1145,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>17</v>
       </c>
@@ -1173,7 +1188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
         <v>19</v>
       </c>
@@ -1201,7 +1216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>11</v>
       </c>
@@ -1229,7 +1244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
         <v>20</v>
       </c>
@@ -1257,7 +1272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
         <v>10</v>
       </c>
@@ -1285,7 +1300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="33" t="s">
         <v>21</v>
       </c>
@@ -1308,12 +1323,12 @@
       <c r="N14" s="6"/>
       <c r="O14" s="7"/>
       <c r="P14" s="8"/>
-      <c r="Q14" s="42">
+      <c r="Q14" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
         <v>3</v>
       </c>
@@ -1334,47 +1349,47 @@
         <v>19664</v>
       </c>
       <c r="F15" s="10">
-        <f>SUM(F3:F13)</f>
+        <f t="shared" ref="F15:P15" si="3">SUM(F3:F13)</f>
         <v>0</v>
       </c>
       <c r="G15" s="11">
-        <f>SUM(G3:G13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H15" s="9">
-        <f>SUM(H3:H13)</f>
+        <f t="shared" si="3"/>
         <v>22545</v>
       </c>
       <c r="I15" s="10">
-        <f>SUM(I3:I13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J15" s="11">
-        <f>SUM(J3:J13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K15" s="9">
-        <f>SUM(K3:K13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L15" s="10">
-        <f>SUM(L3:L13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M15" s="11">
-        <f>SUM(M3:M13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N15" s="9">
-        <f>SUM(N3:N13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="O15" s="10">
-        <f>SUM(O3:O13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="P15" s="11">
-        <f>SUM(P3:P13)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q15" s="12">
